--- a/data/trans_bre/BARTHEL_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/BARTHEL_R2-Edad-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -612,42 +612,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,56</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,81</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,27</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1,34</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>101,86%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-20,47%</t>
         </is>
       </c>
     </row>
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,16; 6,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,94; 8,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,68; 7,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,94; 2,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,83; 350,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,75; 150,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,7; 184,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-75,03; 33,6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -712,42 +712,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,9</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,19</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13,86</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,31</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,28%</t>
         </is>
       </c>
     </row>
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,91; 12,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,97; 22,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,73; 20,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,94; 20,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,56; 115,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,02; 120,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>30,07; 123,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,44; 113,02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -812,42 +812,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,98</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,84</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,37%</t>
         </is>
       </c>
     </row>
@@ -860,565 +860,60 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,99; 8,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,58; 15,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,94; 14,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,58; 10,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,54; 144,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38,02; 131,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,23; 150,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-29,8; 85,63</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>45-54</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-3,56</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-3,81</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-3,27</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1,34</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-3,69%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-4,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-3,47%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-6,96; -0,43</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-8,63; 0,91</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-7,31; 0,48</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-2,13; 5,7</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-7,17; -0,45</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-9,26; 1,0</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-7,61; 0,52</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-2,25; 6,31</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-5,9</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-15,19</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-13,86</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-15,31</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-6,87%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-19,88%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-17,28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-19,58%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-12,15; 1,12</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-22,68; -7,05</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-20,53; -6,33</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-19,9; -10,21</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-13,8; 1,3</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-28,64; -10,3</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-24,81; -8,26</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-24,79; -13,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-5,52</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-10,98</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-9,84</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-5,17</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-5,99%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-12,9%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-11,16%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-5,95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-9,12; -2,15</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-15,71; -5,99</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-14,35; -5,96</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-10,76; 3,32</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-9,75; -2,31</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-17,86; -7,36</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-16,09; -6,9</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-12,32; 3,89</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="6">
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A1:B2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_bre/BARTHEL_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/BARTHEL_R2-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>1,92</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-20,47%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 6,99</t>
+          <t>0,54; 6,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 8,53</t>
+          <t>-1,19; 8,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 7,71</t>
+          <t>-0,84; 6,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 2,0</t>
+          <t>-0,66; 4,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 350,6</t>
+          <t>-0,17; 307,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 150,97</t>
+          <t>-11,0; 152,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 184,58</t>
+          <t>-12,63; 167,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-75,03; 33,6</t>
+          <t>-9,84; 97,68</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,31</t>
+          <t>15,97</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>75,58%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 12,11</t>
+          <t>-0,95; 11,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,97; 22,6</t>
+          <t>7,19; 23,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,73; 20,75</t>
+          <t>7,26; 21,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,94; 20,95</t>
+          <t>10,86; 21,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 115,76</t>
+          <t>-8,61; 108,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,02; 120,81</t>
+          <t>25,07; 121,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,07; 123,37</t>
+          <t>30,63; 131,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,44; 113,02</t>
+          <t>43,8; 117,06</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,17</t>
+          <t>10,38</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>82,0%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 8,99</t>
+          <t>2,41; 9,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,58; 15,74</t>
+          <t>6,34; 15,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,94; 14,47</t>
+          <t>5,36; 13,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 10,68</t>
+          <t>7,29; 13,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,54; 144,47</t>
+          <t>23,43; 143,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,02; 131,05</t>
+          <t>35,77; 131,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,23; 150,4</t>
+          <t>38,08; 131,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-29,8; 85,63</t>
+          <t>51,57; 120,48</t>
         </is>
       </c>
     </row>
